--- a/每日输出/石家庄高短/石家庄-石家庄高短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -768,7 +768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R124"/>
+  <dimension ref="A1:R123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -913,12 +913,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -932,12 +927,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -957,7 +952,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -972,7 +967,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -982,17 +977,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1001,11 +996,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1084,11 +1084,11 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1153,17 +1153,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1172,12 +1172,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1191,12 +1186,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1216,7 +1211,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1231,7 +1226,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1241,17 +1236,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>xieyulong</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>谢宇龙</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,7 +1259,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1274,12 +1269,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>xieyulong</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>谢宇龙</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1314,7 +1309,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1324,17 +1319,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1343,16 +1338,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1362,12 +1357,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1387,7 +1382,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1412,17 +1407,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1450,12 +1445,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1475,7 +1470,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1490,7 +1485,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1500,17 +1495,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>tianmingyang01</t>
+          <t>tianmengjie</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>田名扬</t>
+          <t>田梦洁</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1519,16 +1514,11 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1538,12 +1528,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>tianmingyang01</t>
+          <t>tianmengjie</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>田名扬</t>
+          <t>田梦洁</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1563,7 +1553,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1578,7 +1568,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1588,17 +1578,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>rencan</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>任灿</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1611,7 +1601,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1621,12 +1611,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>rencan</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>任灿</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1646,7 +1636,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1661,7 +1651,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1671,17 +1661,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>wuyawei</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>武亚伟</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,16 +1680,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1709,12 +1699,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>wuyawei</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>武亚伟</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1734,7 +1724,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1749,7 +1739,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1759,17 +1749,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1778,16 +1768,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14,15,17,18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1797,12 +1787,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1822,12 +1812,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1837,7 +1827,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1847,17 +1837,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>gaoke02</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>高科</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1870,7 +1860,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1880,17 +1870,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>gaoke02</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>高科</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1905,7 +1895,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1920,7 +1910,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1930,17 +1920,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1949,16 +1939,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,20,21,22,23</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1968,12 +1958,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1993,7 +1983,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2008,7 +1998,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2018,17 +2008,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>liujiawei</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>刘佳伟</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2037,16 +2027,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2056,12 +2041,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>liujiawei</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>刘佳伟</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2081,7 +2066,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2096,7 +2081,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2106,17 +2091,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>rencan</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>任灿</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2129,7 +2114,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2139,12 +2124,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>rencan</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>任灿</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2164,7 +2149,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2179,7 +2164,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2189,17 +2174,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>新兵营烁-李智慧</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>zhangxinyu</t>
+          <t>hejiaze01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>张欣宇</t>
+          <t>何佳泽</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2208,11 +2193,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10,11,12</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2222,12 +2212,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>zhangxinyu</t>
+          <t>hejiaze01</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>张欣宇</t>
+          <t>何佳泽</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2247,7 +2237,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2262,7 +2252,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2272,17 +2262,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2295,7 +2285,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2305,12 +2295,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2330,7 +2320,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2355,17 +2345,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2374,7 +2364,12 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>9,10,11,13</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2388,12 +2383,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2413,7 +2408,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2428,7 +2423,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2438,17 +2433,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>tianmingyang01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>田名扬</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2457,11 +2452,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>tianmingyang01</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>田名扬</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>zhaoli</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>赵莉</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>zhaoli</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>赵莉</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>gaoke02</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>高科</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2628,11 +2628,16 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2642,12 +2647,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>gaoke02</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>高科</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2667,7 +2672,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2682,7 +2687,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2692,17 +2697,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2711,16 +2716,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>yangmengtao</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>杨梦涛</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2799,11 +2799,16 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2813,17 +2818,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>yangmengtao</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>杨梦涛</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2838,12 +2843,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2853,7 +2858,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2863,17 +2868,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2886,7 +2891,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2896,17 +2901,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2921,7 +2926,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2936,7 +2941,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2946,17 +2951,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>fanjiawei</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>范嘉威</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2969,7 +2974,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2979,12 +2984,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>fanjiawei</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>范嘉威</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3004,7 +3009,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3019,7 +3024,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3029,17 +3034,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3052,7 +3057,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3062,12 +3067,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3087,7 +3092,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3112,17 +3117,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3145,12 +3150,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3170,7 +3175,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3195,17 +3200,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3228,12 +3233,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3253,7 +3258,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3283,12 +3288,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3311,12 +3316,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3336,12 +3341,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3351,7 +3356,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3361,17 +3366,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>zhaoyuanyuan</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>赵园园</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3380,11 +3385,16 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3394,17 +3404,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>zhaoyuanyuan</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>赵园园</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3419,7 +3429,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3434,7 +3444,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3444,17 +3454,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3463,16 +3473,16 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>10,11,12,13</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3482,12 +3492,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3507,7 +3517,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3522,7 +3532,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3532,17 +3542,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>lizihan02</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>李孜涵</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3555,7 +3565,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3565,12 +3575,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>lizihan02</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>李孜涵</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3590,12 +3600,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3605,7 +3615,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3615,17 +3625,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3634,16 +3644,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3653,17 +3658,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3678,7 +3683,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3693,7 +3698,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3703,17 +3708,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>fengguangyuan</t>
+          <t>fanjiawei</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>冯光远</t>
+          <t>范嘉威</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3726,7 +3731,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3736,12 +3741,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>fengguangyuan</t>
+          <t>fanjiawei</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>冯光远</t>
+          <t>范嘉威</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3761,7 +3766,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3791,12 +3796,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3819,12 +3824,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3844,12 +3849,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3859,7 +3864,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3869,17 +3874,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3888,11 +3893,16 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3902,17 +3912,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3927,7 +3937,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3942,7 +3952,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3952,17 +3962,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3975,7 +3985,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3985,12 +3995,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -4010,7 +4020,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4025,7 +4035,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4035,17 +4045,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>新兵营烁-李智慧</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>tianmengjie</t>
+          <t>zhangxinyu</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>田梦洁</t>
+          <t>张欣宇</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4058,7 +4068,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4068,12 +4078,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>tianmengjie</t>
+          <t>zhangxinyu</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>田梦洁</t>
+          <t>张欣宇</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4093,7 +4103,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4108,7 +4118,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4118,17 +4128,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4141,7 +4151,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4151,12 +4161,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4176,7 +4186,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4191,7 +4201,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4201,17 +4211,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4229,7 +4239,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4239,12 +4249,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4264,7 +4274,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4294,12 +4304,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4308,12 +4318,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -4327,12 +4332,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4352,7 +4357,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4367,7 +4372,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4377,17 +4382,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4400,7 +4405,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4410,12 +4415,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4435,7 +4440,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4450,7 +4455,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4460,17 +4465,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>liujiawei</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>刘佳伟</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4479,11 +4484,16 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4493,12 +4503,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>liujiawei</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>刘佳伟</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4518,12 +4528,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4533,7 +4543,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4543,17 +4553,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4562,11 +4572,16 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4576,17 +4591,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4601,7 +4616,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4616,7 +4631,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4626,17 +4641,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4645,11 +4660,16 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4659,12 +4679,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4684,12 +4704,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4709,17 +4729,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4728,11 +4748,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4747,17 +4767,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4772,7 +4792,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4787,7 +4807,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4797,17 +4817,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4816,11 +4836,16 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4830,12 +4855,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4855,7 +4880,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4870,7 +4895,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4880,17 +4905,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4903,7 +4928,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4913,12 +4938,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4938,7 +4963,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4953,7 +4978,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4963,17 +4988,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4982,11 +5007,16 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4996,12 +5026,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -5021,7 +5051,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5036,7 +5066,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5046,17 +5076,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>lijinru02</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>李金儒</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5065,11 +5095,16 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>10,11,12</t>
+        </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5079,12 +5114,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>lijinru02</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>李金儒</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5104,7 +5139,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5119,7 +5154,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5129,17 +5164,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>yangziao</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>杨子澳</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5148,16 +5183,11 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5167,12 +5197,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>yangziao</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>杨子澳</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5192,7 +5222,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5222,12 +5252,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5236,11 +5266,11 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
+          <t>9,10,11</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5255,12 +5285,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5280,12 +5310,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5305,17 +5335,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5324,7 +5354,12 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>9,10,11,12,13</t>
+        </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -5338,17 +5373,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5363,7 +5398,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5378,7 +5413,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5388,17 +5423,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5407,16 +5442,11 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5426,12 +5456,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5451,7 +5481,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5466,7 +5496,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5476,17 +5506,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5495,11 +5525,16 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14</t>
+        </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5509,12 +5544,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5534,7 +5569,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5559,17 +5594,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5597,12 +5632,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5622,7 +5657,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5637,7 +5672,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5647,17 +5682,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>wuqixiang</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>武祺祥</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5666,11 +5701,16 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5680,12 +5720,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>wuqixiang</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>武祺祥</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5705,7 +5745,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5720,7 +5760,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5730,17 +5770,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5749,16 +5789,11 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5768,12 +5803,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5793,7 +5828,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5818,17 +5853,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5851,12 +5886,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5876,12 +5911,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5891,7 +5926,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5901,17 +5936,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5920,16 +5955,11 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5939,17 +5969,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5964,7 +5994,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5979,7 +6009,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5989,17 +6019,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>shenmeng01</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>申萌</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6008,11 +6038,16 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6022,12 +6057,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>shenmeng01</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>申萌</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -6047,12 +6082,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6062,7 +6097,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6072,17 +6107,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6091,16 +6126,16 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6110,17 +6145,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6135,7 +6170,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6150,7 +6185,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6160,17 +6195,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6188,7 +6223,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6198,12 +6233,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6223,7 +6258,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6238,7 +6273,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6248,17 +6283,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>zhangxiying</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>张熙盈</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6267,16 +6302,11 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6286,12 +6316,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>zhangxiying</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>张熙盈</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6311,7 +6341,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6336,17 +6366,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6355,7 +6385,12 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -6369,12 +6404,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6394,12 +6429,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6419,17 +6454,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6438,7 +6473,12 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -6452,17 +6492,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6477,7 +6517,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6492,7 +6532,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6502,17 +6542,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>yangmengtao</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>杨梦涛</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6521,11 +6561,16 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6535,12 +6580,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>yangmengtao</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>杨梦涛</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6560,7 +6605,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6575,7 +6620,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6585,17 +6630,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>yangziao</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>杨子澳</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6604,16 +6649,16 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+          <t>9,10,11,12,22,23</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6623,12 +6668,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>yangziao</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>杨子澳</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6648,12 +6693,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6663,7 +6708,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6673,17 +6718,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>fengguangyuan</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>冯光远</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6692,11 +6737,16 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6706,17 +6756,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>fengguangyuan</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>冯光远</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6731,7 +6781,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6746,7 +6796,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6756,17 +6806,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6775,11 +6825,16 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6789,12 +6844,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6814,12 +6869,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6829,7 +6884,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6839,17 +6894,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6867,7 +6922,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6877,17 +6932,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6902,12 +6957,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6917,7 +6972,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6927,17 +6982,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6946,16 +7001,11 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6965,17 +7015,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6990,7 +7040,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7005,7 +7055,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7015,17 +7065,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7034,11 +7084,16 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7048,12 +7103,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7073,7 +7128,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7088,7 +7143,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7098,17 +7153,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>zhaixinhui</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>翟心惠</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7117,16 +7172,11 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7136,12 +7186,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>zhaixinhui</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>翟心惠</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7161,7 +7211,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7176,7 +7226,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7186,17 +7236,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>wanglijin01</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>王立进</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7205,11 +7255,16 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>11,17</t>
+        </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7219,12 +7274,12 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>wanglijin01</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>王立进</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7244,7 +7299,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7274,12 +7329,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7288,11 +7343,11 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7307,12 +7362,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7332,7 +7387,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7347,7 +7402,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7357,17 +7412,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>lijinru02</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>李金儒</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7380,7 +7435,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7390,12 +7445,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>lijinru02</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>李金儒</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7415,7 +7470,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7430,7 +7485,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7440,17 +7495,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>huangruiqian</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>黄瑞倩</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7459,16 +7514,11 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -7478,12 +7528,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>huangruiqian</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>黄瑞倩</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7503,7 +7553,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7518,7 +7568,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7528,17 +7578,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7551,7 +7601,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -7561,12 +7611,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7586,12 +7636,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7601,7 +7651,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7611,17 +7661,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>wusiqi01</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>吴思琪</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7630,16 +7680,16 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -7649,17 +7699,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>wusiqi01</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>吴思琪</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7674,12 +7724,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7689,7 +7739,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7699,17 +7749,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7718,16 +7768,11 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>13,14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -7737,17 +7782,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7762,7 +7807,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7777,7 +7822,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7787,17 +7832,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7806,11 +7851,16 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
+        </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -7820,12 +7870,12 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -7845,7 +7895,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7860,7 +7910,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7870,17 +7920,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>xieyulong</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>谢宇龙</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7889,11 +7939,16 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -7903,12 +7958,12 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>xieyulong</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>谢宇龙</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -7928,7 +7983,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7943,7 +7998,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7953,17 +8008,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7976,7 +8031,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -7986,12 +8041,12 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -8011,7 +8066,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -8026,7 +8081,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8036,17 +8091,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>wuqixiang</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>武祺祥</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8055,16 +8110,11 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8074,12 +8124,12 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>wuqixiang</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>武祺祥</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -8099,7 +8149,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8129,12 +8179,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8143,12 +8193,7 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -8162,12 +8207,12 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -8187,12 +8232,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8202,7 +8247,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8212,17 +8257,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8231,16 +8276,11 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8250,17 +8290,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8275,7 +8315,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -8290,7 +8330,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8300,17 +8340,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>lizihan02</t>
+          <t>wuyawei</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>李孜涵</t>
+          <t>武亚伟</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8323,7 +8363,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8333,12 +8373,12 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>lizihan02</t>
+          <t>wuyawei</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>李孜涵</t>
+          <t>武亚伟</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -8358,7 +8398,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -8383,17 +8423,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8402,12 +8442,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -8421,12 +8456,12 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -8446,7 +8481,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8471,17 +8506,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>houxinran01</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>侯鑫冉</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8490,7 +8525,12 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -8504,12 +8544,12 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>houxinran01</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>侯鑫冉</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -8529,7 +8569,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8544,7 +8584,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8554,17 +8594,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>shenmeng01</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>申萌</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -8573,16 +8613,11 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -8592,12 +8627,12 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>shenmeng01</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>申萌</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -8617,7 +8652,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8632,7 +8667,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8642,17 +8677,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -8661,11 +8696,16 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
+        </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -8675,12 +8715,12 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -8700,7 +8740,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8715,7 +8755,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8725,17 +8765,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>zhaixinhui</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>翟心惠</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -8748,7 +8788,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -8758,12 +8798,12 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>zhaixinhui</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>翟心惠</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -8783,7 +8823,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8798,7 +8838,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -8808,17 +8848,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8827,16 +8867,11 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -8846,12 +8881,12 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -8871,7 +8906,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8886,7 +8921,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8896,17 +8931,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -8915,11 +8950,16 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>10,11,12,13,14</t>
+        </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -8929,12 +8969,12 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -8954,7 +8994,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8969,7 +9009,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8979,17 +9019,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>liuyifei</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>刘逸飞</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9002,7 +9042,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -9012,12 +9052,12 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>liuyifei</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>刘逸飞</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -9037,7 +9077,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9052,7 +9092,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -9062,17 +9102,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>huangruiqian</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>黄瑞倩</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9081,11 +9121,16 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -9095,12 +9140,12 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>huangruiqian</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>黄瑞倩</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -9120,7 +9165,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9135,7 +9180,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -9145,17 +9190,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -9164,11 +9209,16 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>8,9,10,11</t>
+        </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -9178,12 +9228,12 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -9203,7 +9253,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -9218,7 +9268,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -9228,17 +9278,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9247,16 +9297,11 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -9266,12 +9311,12 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -9291,7 +9336,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9306,7 +9351,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -9316,17 +9361,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>zhangxiying</t>
+          <t>lizuopeng</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>张熙盈</t>
+          <t>李作鹏</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -9339,7 +9384,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -9349,12 +9394,12 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>zhangxiying</t>
+          <t>lizuopeng</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>张熙盈</t>
+          <t>李作鹏</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -9374,7 +9419,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9399,17 +9444,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>武耀巅峰-武亚伟</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>hejiaze01</t>
+          <t>wusiqi01</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>何佳泽</t>
+          <t>吴思琪</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -9418,11 +9463,11 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+          <t>10,11,12,13</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9437,12 +9482,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>hejiaze01</t>
+          <t>wusiqi01</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>何佳泽</t>
+          <t>吴思琪</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -9462,7 +9507,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9477,7 +9522,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -9487,17 +9532,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -9510,7 +9555,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -9520,12 +9565,12 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -9545,7 +9590,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9560,7 +9605,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -9570,17 +9615,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>wangxiaohui</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>王晓慧</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -9589,16 +9634,16 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -9608,12 +9653,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>wangxiaohui</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>王晓慧</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -9633,7 +9678,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9658,17 +9703,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -9677,7 +9722,12 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -9691,12 +9741,12 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -9716,12 +9766,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9741,17 +9791,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -9779,17 +9829,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -9804,7 +9854,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -9829,17 +9879,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -9848,11 +9898,11 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>10,11,12,13</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -9867,12 +9917,12 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -9892,7 +9942,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9907,7 +9957,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -9917,17 +9967,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>武耀巅峰-武亚伟</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>lizuopeng</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>李作鹏</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9940,7 +9990,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -9950,12 +10000,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>lizuopeng</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>李作鹏</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -9975,7 +10025,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10000,17 +10050,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -10019,11 +10069,11 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -10038,12 +10088,12 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -10063,7 +10113,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10078,7 +10128,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -10088,17 +10138,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>liuqingyang</t>
+          <t>liuyifei</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>刘清杨</t>
+          <t>刘逸飞</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -10111,7 +10161,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -10121,12 +10171,12 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>liuqingyang</t>
+          <t>liuyifei</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>刘清杨</t>
+          <t>刘逸飞</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -10146,7 +10196,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10161,7 +10211,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -10171,17 +10221,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>wanglijin01</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>王立进</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -10194,7 +10244,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -10204,12 +10254,12 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>wanglijin01</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>王立进</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -10229,7 +10279,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10254,17 +10304,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>扬帆起航-王泽壮</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -10273,7 +10323,12 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -10287,12 +10342,12 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -10312,12 +10367,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10337,17 +10392,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>zhaoyuanyuan</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>赵园园</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -10370,17 +10425,17 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>zhaoyuanyuan</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>赵园园</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -10395,7 +10450,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -10425,12 +10480,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -10439,12 +10494,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -10458,12 +10508,12 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -10483,12 +10533,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10498,7 +10548,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -10508,17 +10558,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -10527,16 +10577,11 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -10546,17 +10591,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10571,7 +10616,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10586,7 +10631,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -10596,17 +10641,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>zhaoli</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>赵莉</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -10615,16 +10660,16 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12,13</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -10634,12 +10679,12 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>zhaoli</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>赵莉</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -10659,7 +10704,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -10674,7 +10719,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -10684,17 +10729,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>liuqingyang</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>刘清杨</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -10707,7 +10752,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -10717,12 +10762,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>liuqingyang</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>刘清杨</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -10742,7 +10787,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10757,7 +10802,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -10767,17 +10812,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>wangxiaohui</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>王晓慧</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -10786,16 +10831,11 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>13,14,15,16,17,18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -10805,12 +10845,12 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>wangxiaohui</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>王晓慧</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -10830,7 +10870,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10845,7 +10885,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -10855,17 +10895,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -10874,11 +10914,16 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -10888,12 +10933,12 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -10913,7 +10958,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10938,17 +10983,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10957,12 +11002,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>12,13,14,15,16,17,18</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -10976,12 +11016,12 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -11001,7 +11041,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -11016,7 +11056,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -11026,17 +11066,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -11049,7 +11089,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -11059,12 +11099,12 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -11084,7 +11124,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -11099,7 +11139,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -11109,17 +11149,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -11128,16 +11168,11 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -11147,12 +11182,12 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -11172,7 +11207,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -11187,7 +11222,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -11197,17 +11232,17 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>扬帆起航-王泽壮</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -11216,11 +11251,16 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -11230,12 +11270,12 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -11244,89 +11284,6 @@
         </is>
       </c>
       <c r="R123" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>高阶</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>高阶二</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>破浪前行-陈嘉博</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>liuruoling</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>刘若凌</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="K124" t="n">
-        <v>1</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>高二</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>liuruoling</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>刘若凌</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr">
         <is>
           <t>石家庄高短</t>
         </is>
@@ -11502,10 +11459,10 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -11528,10 +11485,10 @@
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -11554,10 +11511,10 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="9">
@@ -11580,10 +11537,10 @@
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -11606,10 +11563,10 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -11632,10 +11589,10 @@
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="12">
@@ -11658,10 +11615,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -11684,10 +11641,10 @@
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="14">
@@ -11707,13 +11664,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
   </sheetData>
@@ -11746,7 +11703,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄高短） 9月9日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄高短） 9月10日</t>
         </is>
       </c>
       <c r="B1" s="7" t="n"/>
@@ -11915,13 +11872,13 @@
         <v>9</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="6">
@@ -11948,13 +11905,13 @@
         <v>19</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" s="21" t="n">
         <v>0.95</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7894736842105263</v>
       </c>
     </row>
     <row r="7">
@@ -12006,10 +11963,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>10</v>
@@ -12039,10 +11996,10 @@
         <v>12</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.9166666666666666</v>
+        <v>8</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0.6666666666666666</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>12</v>
@@ -12072,10 +12029,10 @@
         <v>35</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.6285714285714286</v>
+        <v>18</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>0.5142857142857142</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>35</v>
@@ -12109,25 +12066,25 @@
         <v>8</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0.5</v>
+        <v>5</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.625</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>8</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="14" t="n">
-        <v>0.875</v>
+      <c r="J11" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -12142,10 +12099,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>8</v>
@@ -12175,10 +12132,10 @@
         <v>8</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>8</v>
@@ -12208,25 +12165,25 @@
         <v>24</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="G14" s="16" t="n">
         <v>24</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="J14" s="19" t="n">
-        <v>0.875</v>
+      <c r="J14" s="21" t="n">
+        <v>0.9166666666666666</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -12245,10 +12202,10 @@
         <v>11</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>11</v>
@@ -12278,10 +12235,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>10</v>
@@ -12311,10 +12268,10 @@
         <v>11</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>11</v>
@@ -12344,10 +12301,10 @@
         <v>12</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>0.6666666666666666</v>
+        <v>7</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>0.5833333333333334</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>12</v>
@@ -12377,10 +12334,10 @@
         <v>44</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>0.5681818181818182</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>44</v>
@@ -12414,25 +12371,25 @@
         <v>123</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>0.5772357723577236</v>
+        <v>0.5040650406504065</v>
       </c>
       <c r="G20" s="16" t="n">
         <v>123</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>0.9512195121951219</v>
+        <v>0.959349593495935</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>0.6495726495726496</v>
+        <v>0.652542372881356</v>
       </c>
     </row>
   </sheetData>
@@ -12548,7 +12505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12599,7 +12556,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12650,7 +12607,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12701,7 +12658,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12752,7 +12709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12803,7 +12760,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -12854,7 +12811,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12905,7 +12862,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12956,7 +12913,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -13007,7 +12964,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -13058,7 +13015,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -13095,7 +13052,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -13109,7 +13066,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13160,7 +13117,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13211,7 +13168,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13262,7 +13219,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -13313,7 +13270,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -13364,7 +13321,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -13415,7 +13372,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -13466,7 +13423,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -13517,7 +13474,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13568,7 +13525,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13619,7 +13576,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13670,7 +13627,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13721,7 +13678,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13772,7 +13729,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13823,7 +13780,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13874,7 +13831,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13925,7 +13882,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -13976,7 +13933,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -14027,7 +13984,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -14078,7 +14035,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14129,7 +14086,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14180,7 +14137,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14231,7 +14188,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -14282,7 +14239,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -14333,7 +14290,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -14384,7 +14341,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -14435,7 +14392,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -14486,7 +14443,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14537,7 +14494,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14588,7 +14545,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14639,7 +14596,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14690,7 +14647,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -14741,7 +14698,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14792,7 +14749,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -14843,7 +14800,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -14894,7 +14851,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14945,7 +14902,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -14996,7 +14953,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -15047,7 +15004,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -15098,7 +15055,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -15149,7 +15106,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -15200,7 +15157,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -15251,7 +15208,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -15302,7 +15259,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -15353,7 +15310,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -15404,7 +15361,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15438,7 +15395,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -15455,7 +15412,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15506,7 +15463,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15557,7 +15514,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15608,7 +15565,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -15659,7 +15616,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -15710,7 +15667,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -15761,7 +15718,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -15812,7 +15769,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -15863,7 +15820,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -15914,7 +15871,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -15965,7 +15922,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -16016,7 +15973,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -16067,7 +16024,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -16118,7 +16075,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -16169,7 +16126,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -16220,7 +16177,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -16271,7 +16228,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -16322,7 +16279,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -16373,7 +16330,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -16424,7 +16381,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -16475,7 +16432,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -16526,7 +16483,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -16577,7 +16534,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -16628,7 +16585,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -16679,7 +16636,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -16730,7 +16687,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -16781,7 +16738,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -16832,7 +16789,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -16883,7 +16840,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -16934,7 +16891,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -16985,7 +16942,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -17036,7 +16993,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -17087,7 +17044,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -17138,7 +17095,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -17189,7 +17146,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -17240,7 +17197,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -17291,7 +17248,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -17342,7 +17299,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -17393,7 +17350,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -17444,7 +17401,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -17495,7 +17452,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -17546,7 +17503,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -17597,7 +17554,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -17648,7 +17605,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -17699,7 +17656,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -17750,7 +17707,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -17801,7 +17758,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -17852,7 +17809,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -17903,7 +17860,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -17954,7 +17911,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -18005,7 +17962,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -18056,7 +18013,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -18107,7 +18064,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -18158,7 +18115,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -18209,7 +18166,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -18260,7 +18217,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -18311,7 +18268,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -18362,7 +18319,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -18413,7 +18370,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -18464,7 +18421,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -18515,7 +18472,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -18566,7 +18523,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -18617,7 +18574,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -18668,7 +18625,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -18719,7 +18676,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -18910,13 +18867,13 @@
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="5">
@@ -19035,16 +18992,16 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
